--- a/Dokumentation/Leistungsaufnahme 5V Schaltung.xlsx
+++ b/Dokumentation/Leistungsaufnahme 5V Schaltung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Documents\Uni\Semester 6\Projektarbeit\active-balancing\Dokumentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613DA395-0AC2-4952-96FD-499D95D532B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EA50EF-9D1D-4CB2-BAD8-3AF2CAD3AEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{CAA5690E-E7E9-408F-8A2E-5DFFF73490A4}"/>
+    <workbookView xWindow="3360" yWindow="2880" windowWidth="19200" windowHeight="11170" xr2:uid="{CAA5690E-E7E9-408F-8A2E-5DFFF73490A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -101,9 +101,6 @@
     <t>maximal 50 mA, typisch 10-20mA</t>
   </si>
   <si>
-    <t>Mit 680 Ohm Vorwiderstand, ULED = 1.2V, I = 5.6mA</t>
-  </si>
-  <si>
     <t>DAC</t>
   </si>
   <si>
@@ -150,6 +147,9 @@
   </si>
   <si>
     <t>maximal 1W möglich</t>
+  </si>
+  <si>
+    <t>Mit 330 Ohm Vorwiderstand, ULED = 1.2V, I = 12mA + 330Ohm * 12mA^2</t>
   </si>
 </sst>
 </file>
@@ -205,9 +205,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -245,7 +245,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -351,7 +351,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -493,7 +493,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -595,22 +595,22 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="F8" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="L8">
-        <f>1.2*0.0056</f>
-        <v>6.7199999999999994E-3</v>
+        <f>1.2*0.012+330*0.012^2</f>
+        <v>6.1920000000000003E-2</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>23</v>
       </c>
       <c r="L9">
         <f>5*400*10^-6</f>
@@ -619,35 +619,35 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
         <v>25</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" t="s">
         <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" t="s">
         <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>32</v>
       </c>
       <c r="L12">
         <f>5*10*10^-6</f>
@@ -656,10 +656,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
         <v>33</v>
-      </c>
-      <c r="F13" t="s">
-        <v>34</v>
       </c>
       <c r="L13">
         <f>5*0.03</f>
@@ -668,14 +668,14 @@
     </row>
     <row r="20" spans="12:14" x14ac:dyDescent="0.35">
       <c r="L20">
-        <f>SUM(L3:L19)</f>
-        <v>0.19681999999999999</v>
+        <f>SUM(L3:L12)</f>
+        <v>0.10202</v>
       </c>
       <c r="M20" t="s">
+        <v>34</v>
+      </c>
+      <c r="N20" t="s">
         <v>35</v>
-      </c>
-      <c r="N20" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
